--- a/AAII_Financials/Quarterly/ULS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ULS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
   <si>
     <t>ULS</t>
   </si>
@@ -656,250 +656,263 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>816000</v>
+      </c>
+      <c r="E8" s="3">
         <v>758000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>789000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>783000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>776000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>705000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>739000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>731000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>730000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>670000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>684000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>676000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>689000</v>
-      </c>
-      <c r="P8" s="3">
-        <v>629000</v>
       </c>
       <c r="Q8" s="3">
         <v>629000</v>
       </c>
       <c r="R8" s="3">
+        <v>629000</v>
+      </c>
+      <c r="S8" s="3">
         <v>623000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>645000</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>399000</v>
+      </c>
+      <c r="E9" s="3">
         <v>377000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>397000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>389000</v>
       </c>
-      <c r="G9" s="3">
-        <v>393000</v>
-      </c>
       <c r="H9" s="3">
+        <v>394000</v>
+      </c>
+      <c r="I9" s="3">
         <v>365000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>390000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>373000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>364000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>351000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>367000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>344000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>352000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>335000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>317000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>329000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>417000</v>
+      </c>
+      <c r="E10" s="3">
         <v>381000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>392000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>394000</v>
       </c>
-      <c r="G10" s="3">
-        <v>383000</v>
-      </c>
       <c r="H10" s="3">
+        <v>382000</v>
+      </c>
+      <c r="I10" s="3">
         <v>340000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>349000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>358000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>366000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>319000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>317000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>332000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>337000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>294000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>312000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>294000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>302000</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -919,44 +932,45 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
         <v>65000</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3">
         <v>59000</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="3">
         <v>51000</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
@@ -972,8 +986,11 @@
       <c r="S12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1025,19 +1042,22 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>-191000</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
         <v>35000</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
@@ -1049,26 +1069,26 @@
         <v>-1000</v>
       </c>
       <c r="J14" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="K14" s="3">
         <v>1000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-25000</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>-2000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>35000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-5000</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1078,61 +1098,67 @@
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E15" s="3">
         <v>47000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>30800</v>
-      </c>
-      <c r="F15" s="3">
-        <v>46000</v>
       </c>
       <c r="G15" s="3">
         <v>46000</v>
       </c>
       <c r="H15" s="3">
+        <v>46000</v>
+      </c>
+      <c r="I15" s="3">
         <v>45000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>28300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>43000</v>
-      </c>
-      <c r="K15" s="3">
-        <v>41000</v>
       </c>
       <c r="L15" s="3">
         <v>41000</v>
       </c>
       <c r="M15" s="3">
+        <v>41000</v>
+      </c>
+      <c r="N15" s="3">
         <v>25800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>37000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>38000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>36000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1149,114 +1175,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>666000</v>
+      </c>
+      <c r="E17" s="3">
         <v>621000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>637000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>628000</v>
       </c>
-      <c r="G17" s="3">
-        <v>638000</v>
-      </c>
       <c r="H17" s="3">
+        <v>639000</v>
+      </c>
+      <c r="I17" s="3">
         <v>598000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>626000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>603000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>606000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>581000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>600000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>552000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>574000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>556000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>537000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>508000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>543000</v>
       </c>
     </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>150000</v>
+      </c>
+      <c r="E18" s="3">
         <v>137000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>152000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>155000</v>
       </c>
-      <c r="G18" s="3">
-        <v>138000</v>
-      </c>
       <c r="H18" s="3">
+        <v>137000</v>
+      </c>
+      <c r="I18" s="3">
         <v>107000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>113000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>128000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>124000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>89000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>84000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>124000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>115000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>73000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>92000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>115000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>102000</v>
       </c>
     </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1276,273 +1309,289 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>1000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>4000</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>4000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>10000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>10000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-6000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>33000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-21000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-11000</v>
       </c>
     </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>196000</v>
+      </c>
+      <c r="E21" s="3">
         <v>183000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>178800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>201000</v>
       </c>
-      <c r="G21" s="3">
-        <v>180000</v>
-      </c>
       <c r="H21" s="3">
+        <v>179000</v>
+      </c>
+      <c r="I21" s="3">
         <v>149000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>131300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>173000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>162000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>128000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>108800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>151000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>159000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>116000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>158000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>128000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>124000</v>
       </c>
     </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E22" s="3">
         <v>8000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>9000</v>
-      </c>
-      <c r="F22" s="3">
-        <v>10000</v>
       </c>
       <c r="G22" s="3">
         <v>10000</v>
       </c>
       <c r="H22" s="3">
+        <v>10000</v>
+      </c>
+      <c r="I22" s="3">
         <v>12000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>13000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>14000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>13000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>15000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>12000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>7000</v>
-      </c>
-      <c r="O22" s="3">
-        <v>8000</v>
       </c>
       <c r="P22" s="3">
         <v>8000</v>
       </c>
       <c r="Q22" s="3">
+        <v>8000</v>
+      </c>
+      <c r="R22" s="3">
         <v>30000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>5000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>338000</v>
+      </c>
+      <c r="E23" s="3">
         <v>129000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>105000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>146000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>125000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>94000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>92000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>116000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>134000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>73000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>79000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>75000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>120000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>72000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>95000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>89000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>88000</v>
       </c>
     </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>84000</v>
+      </c>
+      <c r="E24" s="3">
         <v>32000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>34000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>40000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>28000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>23000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>7000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>22000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>28000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>13000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>17000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>18000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>21000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>14000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>13000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>16000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1594,114 +1643,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>254000</v>
+      </c>
+      <c r="E26" s="3">
         <v>97000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>71000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>106000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>97000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>71000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>85000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>94000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>106000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>60000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>62000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>57000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>99000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>58000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>82000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>73000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>65000</v>
       </c>
     </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>246000</v>
+      </c>
+      <c r="E27" s="3">
         <v>92000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>67000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>100000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>91000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>67000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>81000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>88000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>101000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>56000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>58000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>53000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>94000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>55000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>78000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>70000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1753,8 +1811,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1806,8 +1867,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1859,8 +1923,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1912,114 +1979,123 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-4000</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>-4000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-10000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-10000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>6000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>7000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-33000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>21000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>11000</v>
       </c>
     </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>246000</v>
+      </c>
+      <c r="E33" s="3">
         <v>92000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>67000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>100000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>91000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>67000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>81000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>88000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>101000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>56000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>58000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>53000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>94000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>55000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>78000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>70000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2071,119 +2147,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>246000</v>
+      </c>
+      <c r="E35" s="3">
         <v>92000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>67000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>100000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>91000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>67000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>81000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>88000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>101000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>56000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>58000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>53000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>94000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>55000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>78000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>70000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2203,8 +2288,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2224,61 +2310,65 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>434000</v>
+      </c>
+      <c r="E41" s="3">
         <v>258000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>295000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>255000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>272000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>267000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>298000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>327000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>295000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>344000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>315000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>457000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>413000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>418000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>322000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>393000</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2316,75 +2406,81 @@
         <v>0</v>
       </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>27000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>65000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>51000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>28000</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>710000</v>
+      </c>
+      <c r="E43" s="3">
         <v>719000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>626000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>623000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>648000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>666000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>562000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>603000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>610000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>622000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>590000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>540000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>562000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>601000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>547000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>524000</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2427,8 +2523,8 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -2436,119 +2532,128 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>90000</v>
+      </c>
+      <c r="E45" s="3">
         <v>70000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>79000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>117000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>89000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>65000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>61000</v>
-      </c>
-      <c r="J45" s="3">
-        <v>4000</v>
       </c>
       <c r="K45" s="3">
         <v>4000</v>
       </c>
       <c r="L45" s="3">
+        <v>4000</v>
+      </c>
+      <c r="M45" s="3">
         <v>85000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>13000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>88000</v>
-      </c>
-      <c r="O45" s="3">
-        <v>5000</v>
       </c>
       <c r="P45" s="3">
         <v>5000</v>
       </c>
       <c r="Q45" s="3">
+        <v>5000</v>
+      </c>
+      <c r="R45" s="3">
         <v>78000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>71000</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1234000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1047000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1000000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>995000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1009000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>998000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>921000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>977000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>957000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1051000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>953000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1085000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1114000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1174000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>998000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1016000</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>33000</v>
+        <v>55000</v>
       </c>
       <c r="E47" s="3">
         <v>33000</v>
@@ -2560,13 +2665,13 @@
         <v>33000</v>
       </c>
       <c r="H47" s="3">
-        <v>36000</v>
+        <v>33000</v>
       </c>
       <c r="I47" s="3">
         <v>36000</v>
       </c>
       <c r="J47" s="3">
-        <v>42000</v>
+        <v>36000</v>
       </c>
       <c r="K47" s="3">
         <v>42000</v>
@@ -2578,131 +2683,140 @@
         <v>42000</v>
       </c>
       <c r="N47" s="3">
+        <v>42000</v>
+      </c>
+      <c r="O47" s="3">
         <v>65000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>64000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>63000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>62000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>64000</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>932000</v>
+      </c>
+      <c r="E48" s="3">
         <v>884000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>878000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>847000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>837000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>813000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>817000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>785000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>699000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>702000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>706000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>651000</v>
-      </c>
-      <c r="O48" s="3">
-        <v>652000</v>
       </c>
       <c r="P48" s="3">
         <v>652000</v>
       </c>
       <c r="Q48" s="3">
+        <v>652000</v>
+      </c>
+      <c r="R48" s="3">
         <v>637000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>600000</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>773000</v>
+      </c>
+      <c r="E49" s="3">
         <v>780000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>809000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>818000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>830000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>820000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>818000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>845000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>826000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>820000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>834000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>828000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>855000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>852000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>847000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>803000</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2754,8 +2868,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2807,61 +2924,67 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>79000</v>
+      </c>
+      <c r="E52" s="3">
         <v>119000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>107000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>106000</v>
-      </c>
-      <c r="G52" s="3">
-        <v>103000</v>
       </c>
       <c r="H52" s="3">
         <v>103000</v>
       </c>
       <c r="I52" s="3">
+        <v>103000</v>
+      </c>
+      <c r="J52" s="3">
         <v>100000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>108000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>100000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>92000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>91000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>60000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>55000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>50000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>176000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>171000</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2913,61 +3036,67 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3119000</v>
+      </c>
+      <c r="E54" s="3">
         <v>2955000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2921000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2898000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2922000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2878000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2800000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2877000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2742000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2819000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2736000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2806000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2841000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2908000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2720000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2654000</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2987,8 +3116,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3008,326 +3138,345 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>179000</v>
+      </c>
+      <c r="E57" s="3">
         <v>168000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>183000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>151000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>139000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>143000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>182000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>138000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>134000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>156000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>169000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>128000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>125000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>128000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>153000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>141000</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E58" s="3">
         <v>41000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>43000</v>
-      </c>
-      <c r="F58" s="3">
-        <v>42000</v>
       </c>
       <c r="G58" s="3">
         <v>42000</v>
       </c>
       <c r="H58" s="3">
+        <v>42000</v>
+      </c>
+      <c r="I58" s="3">
         <v>40000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>88000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>74000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>36000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>37000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>39000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>38000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>39000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>41000</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>452000</v>
+      </c>
+      <c r="E59" s="3">
         <v>502000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>252000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>302000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>376000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>457000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>216000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>310000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>399000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>466000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>220000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>272000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>350000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>402000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>541000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>558000</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>866000</v>
+      </c>
+      <c r="E60" s="3">
         <v>899000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>760000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>749000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>765000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>804000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>740000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>745000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>740000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>829000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>709000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>676000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>735000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>819000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>694000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>699000</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>437000</v>
+      </c>
+      <c r="E61" s="3">
         <v>498000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>640000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>694000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>763000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>803000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>847000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>913000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>902000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>983000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1024000</v>
-      </c>
-      <c r="N61" s="3">
-        <v>610000</v>
       </c>
       <c r="O61" s="3">
         <v>610000</v>
       </c>
       <c r="P61" s="3">
+        <v>610000</v>
+      </c>
+      <c r="Q61" s="3">
         <v>643000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>499000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>574000</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>93000</v>
+      </c>
+      <c r="E62" s="3">
         <v>97000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>74000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>89000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>79000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>92000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>63000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>101000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>91000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>97000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>93000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>80000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>78000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>73000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>450000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>446000</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3379,8 +3528,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3432,8 +3584,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3485,61 +3640,67 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1499000</v>
+      </c>
+      <c r="E66" s="3">
         <v>1619000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1627000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1678000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1809000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1894000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1869000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1981000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1956000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2136000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2058000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1609000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1666000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1786000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1666000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1738000</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3559,8 +3720,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3612,8 +3774,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3665,8 +3830,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3718,8 +3886,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3771,61 +3942,67 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>750000</v>
+      </c>
+      <c r="E72" s="3">
         <v>533000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>470000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>429000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>356000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>291000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>250000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>194000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>131000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>55000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>24000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>353000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>320000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>246000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>211000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>133000</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3877,8 +4054,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3930,8 +4110,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3983,61 +4166,67 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1595000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1319000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1262000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1193000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1093000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>970000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>904000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>872000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>769000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>671000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>654000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1178000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1160000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1096000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1054000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>916000</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4089,119 +4278,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>246000</v>
+      </c>
+      <c r="E81" s="3">
         <v>92000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>67000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>100000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>91000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>67000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>81000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>88000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>101000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>56000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>58000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>53000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>94000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>55000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>78000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>70000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4221,61 +4419,65 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>43000</v>
+      </c>
+      <c r="E83" s="3">
         <v>42000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>-12000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>39000</v>
-      </c>
-      <c r="G83" s="3">
-        <v>38000</v>
       </c>
       <c r="H83" s="3">
         <v>38000</v>
       </c>
       <c r="I83" s="3">
+        <v>38000</v>
+      </c>
+      <c r="J83" s="3">
         <v>-8000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>33000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>34000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>32000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>-10000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>30000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>29000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>30000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>33000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>34000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>33000</v>
       </c>
     </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4327,8 +4529,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4380,8 +4585,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4433,8 +4641,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4486,8 +4697,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4539,61 +4753,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>160000</v>
+      </c>
+      <c r="E89" s="3">
         <v>219000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>144000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>155000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>147000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>154000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>130000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>150000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>103000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>141000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>126000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>121000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>59000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>161000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>80000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>131000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>56000</v>
       </c>
     </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4613,8 +4833,9 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4622,52 +4843,55 @@
         <v>-69000</v>
       </c>
       <c r="E91" s="3">
+        <v>-69000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-58000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-46000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-42000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-51000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-58000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-66000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-56000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-57000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-59000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-43000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-50000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-63000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-46000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-41000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-34000</v>
       </c>
     </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4719,8 +4943,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4772,61 +4999,67 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>131000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-61000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-21000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-76000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-57000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-50000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-59000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-82000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-36000</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-57000</v>
       </c>
       <c r="M94" s="3">
         <v>-57000</v>
       </c>
       <c r="N94" s="3">
+        <v>-57000</v>
+      </c>
+      <c r="O94" s="3">
         <v>-33000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-10000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-75000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-90000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-70000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-12000</v>
       </c>
     </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4846,8 +5079,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4855,7 +5089,7 @@
         <v>29000</v>
       </c>
       <c r="E96" s="3">
-        <v>26000</v>
+        <v>29000</v>
       </c>
       <c r="F96" s="3">
         <v>26000</v>
@@ -4867,7 +5101,7 @@
         <v>26000</v>
       </c>
       <c r="I96" s="3">
-        <v>25000</v>
+        <v>26000</v>
       </c>
       <c r="J96" s="3">
         <v>25000</v>
@@ -4879,7 +5113,7 @@
         <v>25000</v>
       </c>
       <c r="M96" s="3">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="N96" s="3">
         <v>20000</v>
@@ -4891,7 +5125,7 @@
         <v>20000</v>
       </c>
       <c r="Q96" s="3">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -4899,8 +5133,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4952,8 +5189,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5005,8 +5245,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5058,163 +5301,175 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-114000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-194000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-82000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-93000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-86000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-135000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-82000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-43000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-110000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-49000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-219000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-36000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-49000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>10000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-74000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-99000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E101" s="3">
+      <c r="D101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3">
         <v>-18000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>7000</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-6000</v>
       </c>
       <c r="H101" s="3">
         <v>-6000</v>
       </c>
       <c r="I101" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="J101" s="3">
         <v>8000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-8000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-5000</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N101" s="3">
         <v>13000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-17000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-20000</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R101" s="3">
         <v>13000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-17000</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>176000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-37000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>40000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-17000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>5000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-31000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-29000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>32000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-49000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>29000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-142000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>44000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-5000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>96000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-71000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-55000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>28000</v>
       </c>
     </row>
